--- a/templates/sites-template.xlsx
+++ b/templates/sites-template.xlsx
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -664,13 +664,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Note</v>
+        <v>City</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>A line under the table. Add more Note rows for more lines</v>
+        <v>A blue city marker with its name, written as Name: coordinates, e.g. Manesar: 28.3540, 76.9395. Add more City rows for more cities</v>
       </c>
     </row>
     <row r="18">
@@ -681,12 +681,23 @@
         <v/>
       </c>
       <c r="C18" t="str">
+        <v>A line under the table. Add more Note rows for more lines</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Note</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
